--- a/public/Orders.xlsx
+++ b/public/Orders.xlsx
@@ -1,41 +1,266 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhi singh\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C46EA821-469F-4676-B1CB-53356E397E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Orders" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="78">
+  <si>
+    <t>order_id</t>
+  </si>
+  <si>
+    <t>fullname</t>
+  </si>
+  <si>
+    <t>phonenumber</t>
+  </si>
+  <si>
+    <t>alternatephonenumber</t>
+  </si>
+  <si>
+    <t>consigneecompany</t>
+  </si>
+  <si>
+    <t>gstin</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>fulladdress</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>state</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>pincode</t>
+  </si>
+  <si>
+    <t>landmark</t>
+  </si>
+  <si>
+    <t>billing_is_same_as_consignee</t>
+  </si>
+  <si>
+    <t>billing_full_name</t>
+  </si>
+  <si>
+    <t>billing_phone</t>
+  </si>
+  <si>
+    <t>billing_email</t>
+  </si>
+  <si>
+    <t>billing_address</t>
+  </si>
+  <si>
+    <t>billing_landmark</t>
+  </si>
+  <si>
+    <t>billing_pincode</t>
+  </si>
+  <si>
+    <t>billing_city</t>
+  </si>
+  <si>
+    <t>billing_state</t>
+  </si>
+  <si>
+    <t>billing_country</t>
+  </si>
+  <si>
+    <t>pickup_location_name</t>
+  </si>
+  <si>
+    <t>pickup_person_name</t>
+  </si>
+  <si>
+    <t>pickup_person_phone</t>
+  </si>
+  <si>
+    <t>pickup_person_email</t>
+  </si>
+  <si>
+    <t>pickup_address</t>
+  </si>
+  <si>
+    <t>pickup_landmark</t>
+  </si>
+  <si>
+    <t>pickup_country</t>
+  </si>
+  <si>
+    <t>pickup_state</t>
+  </si>
+  <si>
+    <t>pickup_city</t>
+  </si>
+  <si>
+    <t>pickup_location_code</t>
+  </si>
+  <si>
+    <t>pickup_account_id</t>
+  </si>
+  <si>
+    <t>isOtherField</t>
+  </si>
+  <si>
+    <t>isActive</t>
+  </si>
+  <si>
+    <t>pickup_pincode</t>
+  </si>
+  <si>
+    <t>channel</t>
+  </si>
+  <si>
+    <t>productDetails</t>
+  </si>
+  <si>
+    <t>payment_mode</t>
+  </si>
+  <si>
+    <t>total_amount</t>
+  </si>
+  <si>
+    <t>order_value</t>
+  </si>
+  <si>
+    <t>tax_amount</t>
+  </si>
+  <si>
+    <t>discount</t>
+  </si>
+  <si>
+    <t>gift_wrap_charges</t>
+  </si>
+  <si>
+    <t>other_charges</t>
+  </si>
+  <si>
+    <t>cod_charges</t>
+  </si>
+  <si>
+    <t>shipping_charges</t>
+  </si>
+  <si>
+    <t>dead_weight</t>
+  </si>
+  <si>
+    <t>volumetric_weigth</t>
+  </si>
+  <si>
+    <t>length</t>
+  </si>
+  <si>
+    <t>breath</t>
+  </si>
+  <si>
+    <t>height</t>
+  </si>
+  <si>
+    <t>account_id</t>
+  </si>
+  <si>
+    <t>order_status</t>
+  </si>
+  <si>
+    <t>Rishikesh Kumar Singh</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>john electronics</t>
+  </si>
+  <si>
+    <t>11AAAAA0000A1Z5</t>
+  </si>
+  <si>
+    <t>rishikeshkumarsingh810@gmail.com</t>
+  </si>
+  <si>
+    <t>Sector 6 Road, 3rd Floor, Plot No. 10, LSC-02, Sector 06, Dwarka, Delhi 110075, IN</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Delhi</t>
+  </si>
+  <si>
+    <t>South West Delhi</t>
+  </si>
+  <si>
+    <t>CSB LAYOUT BANGALORE</t>
+  </si>
+  <si>
+    <t>distributions center</t>
+  </si>
+  <si>
+    <t>1234567890</t>
+  </si>
+  <si>
+    <t>09, Lekha Nagar, Khagaul, Patna, Bihar 801505, India</t>
+  </si>
+  <si>
+    <t>NEAR GRAHAK SEVA KENDRA SBI</t>
+  </si>
+  <si>
+    <t>Bihar</t>
+  </si>
+  <si>
+    <t>Patna</t>
+  </si>
+  <si>
+    <t>1e601279-6f09-4d87-93dd-cf4c3e7fff10</t>
+  </si>
+  <si>
+    <t>801505</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>[{"name":"Boult Astra with Quad Mic ENC, 48Hrs Battery, Low Latency Gaming, Made in India, 5.3v Bluetooth  (White Opal, True Wireless)","price":2000,"hsn_code":87654321,"category":"Nutritional Supplements","brand":"","expiry_date":"2025-12-19","batch_no":"20230101-L01","images":[],"dead_weigth":"","volumetric_weigth":"","length":"","breath":"","height":"","quantity":10,"isSensitiveOrder":true,"sku_code":"sku_code1"}]</t>
+  </si>
+  <si>
+    <t>prepaid</t>
+  </si>
+  <si>
+    <t>new</t>
+  </si>
+  <si>
+    <t>order 12:3452</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +290,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,297 +629,385 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AM2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:BC2"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="25.83203125" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="30.83203125" customWidth="1"/>
-    <col min="7" max="7" width="40.83203125" customWidth="1"/>
-    <col min="8" max="8" width="20.83203125" customWidth="1"/>
-    <col min="9" max="9" width="10.83203125" customWidth="1"/>
-    <col min="10" max="10" width="15.83203125" customWidth="1"/>
-    <col min="11" max="11" width="15.83203125" customWidth="1"/>
-    <col min="12" max="12" width="10.83203125" customWidth="1"/>
-    <col min="13" max="13" width="15.83203125" customWidth="1"/>
-    <col min="14" max="14" width="15.83203125" customWidth="1"/>
-    <col min="15" max="15" width="50.83203125" customWidth="1"/>
-    <col min="16" max="16" width="10.83203125" customWidth="1"/>
-    <col min="17" max="17" width="15.83203125" customWidth="1"/>
-    <col min="18" max="18" width="15.83203125" customWidth="1"/>
-    <col min="19" max="19" width="10.83203125" customWidth="1"/>
-    <col min="20" max="20" width="15.83203125" customWidth="1"/>
-    <col min="21" max="21" width="15.83203125" customWidth="1"/>
-    <col min="22" max="22" width="15.83203125" customWidth="1"/>
-    <col min="23" max="23" width="15.83203125" customWidth="1"/>
-    <col min="24" max="24" width="15.83203125" customWidth="1"/>
-    <col min="25" max="25" width="25.83203125" customWidth="1"/>
-    <col min="26" max="26" width="20.83203125" customWidth="1"/>
-    <col min="27" max="27" width="15.83203125" customWidth="1"/>
-    <col min="28" max="28" width="20.83203125" customWidth="1"/>
-    <col min="29" max="29" width="25.83203125" customWidth="1"/>
-    <col min="30" max="30" width="15.83203125" customWidth="1"/>
-    <col min="31" max="31" width="30.83203125" customWidth="1"/>
-    <col min="32" max="32" width="40.83203125" customWidth="1"/>
-    <col min="33" max="33" width="20.83203125" customWidth="1"/>
-    <col min="34" max="34" width="10.83203125" customWidth="1"/>
-    <col min="35" max="35" width="15.83203125" customWidth="1"/>
-    <col min="36" max="36" width="15.83203125" customWidth="1"/>
-    <col min="37" max="37" width="10.83203125" customWidth="1"/>
-    <col min="38" max="38" width="15.83203125" customWidth="1"/>
-    <col min="39" max="39" width="15.83203125" customWidth="1"/>
-    <col min="40" max="40" width="50.83203125" customWidth="1"/>
-    <col min="41" max="41" width="10.83203125" customWidth="1"/>
-    <col min="42" max="42" width="15.83203125" customWidth="1"/>
-    <col min="43" max="43" width="15.83203125" customWidth="1"/>
-    <col min="44" max="44" width="10.83203125" customWidth="1"/>
-    <col min="45" max="45" width="15.83203125" customWidth="1"/>
+    <col min="1" max="1" width="20.796875" customWidth="1"/>
+    <col min="2" max="2" width="15.796875" customWidth="1"/>
+    <col min="3" max="3" width="20.796875" customWidth="1"/>
+    <col min="4" max="4" width="25.796875" customWidth="1"/>
+    <col min="5" max="5" width="15.796875" customWidth="1"/>
+    <col min="6" max="6" width="30.796875" customWidth="1"/>
+    <col min="7" max="7" width="40.796875" customWidth="1"/>
+    <col min="8" max="8" width="20.796875" customWidth="1"/>
+    <col min="9" max="9" width="10.796875" customWidth="1"/>
+    <col min="10" max="11" width="15.796875" customWidth="1"/>
+    <col min="12" max="12" width="10.796875" customWidth="1"/>
+    <col min="13" max="14" width="15.796875" customWidth="1"/>
+    <col min="15" max="15" width="50.796875" customWidth="1"/>
+    <col min="16" max="16" width="10.796875" customWidth="1"/>
+    <col min="17" max="18" width="15.796875" customWidth="1"/>
+    <col min="19" max="19" width="10.796875" customWidth="1"/>
+    <col min="20" max="24" width="15.796875" customWidth="1"/>
+    <col min="25" max="25" width="25.796875" customWidth="1"/>
+    <col min="26" max="26" width="20.796875" customWidth="1"/>
+    <col min="27" max="27" width="15.796875" customWidth="1"/>
+    <col min="28" max="28" width="20.796875" customWidth="1"/>
+    <col min="29" max="29" width="25.796875" customWidth="1"/>
+    <col min="30" max="30" width="15.796875" customWidth="1"/>
+    <col min="31" max="31" width="30.796875" customWidth="1"/>
+    <col min="32" max="32" width="40.796875" customWidth="1"/>
+    <col min="33" max="33" width="20.796875" customWidth="1"/>
+    <col min="34" max="34" width="10.796875" customWidth="1"/>
+    <col min="35" max="36" width="15.796875" customWidth="1"/>
+    <col min="37" max="37" width="10.796875" customWidth="1"/>
+    <col min="38" max="39" width="15.796875" customWidth="1"/>
+    <col min="40" max="40" width="50.796875" customWidth="1"/>
+    <col min="41" max="41" width="10.796875" customWidth="1"/>
+    <col min="42" max="43" width="15.796875" customWidth="1"/>
+    <col min="44" max="44" width="10.796875" customWidth="1"/>
+    <col min="45" max="45" width="15.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>consignee_person_name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>consignee_person_phone</v>
-      </c>
-      <c r="C1" t="str">
-        <v>consignee_person_alterPhonenumber</v>
-      </c>
-      <c r="D1" t="str">
-        <v>consignee_person_consigneecompany</v>
-      </c>
-      <c r="E1" t="str">
-        <v>consignee_person_gstin</v>
-      </c>
-      <c r="F1" t="str">
-        <v>consignee_person_email</v>
-      </c>
-      <c r="G1" t="str">
-        <v>consignee_person_fulladdress</v>
-      </c>
-      <c r="H1" t="str">
-        <v>consignee_person_country</v>
-      </c>
-      <c r="I1" t="str">
-        <v>consignee_person_state</v>
-      </c>
-      <c r="J1" t="str">
-        <v>consignee_person_city</v>
-      </c>
-      <c r="K1" t="str">
-        <v>consignee_person_pincode</v>
-      </c>
-      <c r="L1" t="str">
-        <v>consignee_person_landmark</v>
-      </c>
-      <c r="M1" t="str">
-        <v>pickup_person_name</v>
-      </c>
-      <c r="N1" t="str">
-        <v>pickup_person_phone</v>
-      </c>
-      <c r="O1" t="str">
-        <v>pickup_person_email</v>
-      </c>
-      <c r="P1" t="str">
-        <v>pickup_address</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>pickup_landmark</v>
-      </c>
-      <c r="R1" t="str">
-        <v>pickup_country</v>
-      </c>
-      <c r="S1" t="str">
-        <v>pickup_state</v>
-      </c>
-      <c r="T1" t="str">
-        <v>pickup_city</v>
-      </c>
-      <c r="U1" t="str">
-        <v>pickup_pincode</v>
-      </c>
-      <c r="V1" t="str">
-        <v>orderid</v>
-      </c>
-      <c r="W1" t="str">
-        <v>channel</v>
-      </c>
-      <c r="X1" t="str">
-        <v>productDetails</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>payment_mode</v>
-      </c>
-      <c r="Z1" t="str">
-        <v>total_amount</v>
-      </c>
-      <c r="AA1" t="str">
-        <v>order_value</v>
-      </c>
-      <c r="AB1" t="str">
-        <v>tax_amount</v>
-      </c>
-      <c r="AC1" t="str">
-        <v>discount</v>
-      </c>
-      <c r="AD1" t="str">
-        <v>gift_wrap_charges</v>
-      </c>
-      <c r="AE1" t="str">
-        <v>other_charges</v>
-      </c>
-      <c r="AF1" t="str">
-        <v>cod_charges</v>
-      </c>
-      <c r="AG1" t="str">
-        <v>shipping_charges</v>
-      </c>
-      <c r="AH1" t="str">
-        <v>dead_weight</v>
-      </c>
-      <c r="AI1" t="str">
-        <v>volumetric_weigth</v>
-      </c>
-      <c r="AJ1" t="str">
-        <v>length</v>
-      </c>
-      <c r="AK1" t="str">
-        <v>breath</v>
-      </c>
-      <c r="AL1" t="str">
-        <v>height</v>
-      </c>
-      <c r="AM1" t="str">
-        <v>order_status</v>
+    <row r="1" spans="1:55" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Rishikesh Kumar Singh</v>
-      </c>
-      <c r="B2">
-        <v>6207654176</v>
+    <row r="2" spans="1:55" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" t="s">
+        <v>55</v>
       </c>
       <c r="C2">
-        <v>9835354290</v>
-      </c>
-      <c r="D2" t="str">
-        <v>rishu clothes</v>
-      </c>
-      <c r="E2" t="str">
-        <v>11AAAAA0000A1Z5</v>
-      </c>
-      <c r="F2" t="str">
-        <v>xyz@gmail.com</v>
-      </c>
-      <c r="G2" t="str">
-        <v>testing address</v>
-      </c>
-      <c r="H2" t="str">
-        <v>India</v>
-      </c>
-      <c r="I2" t="str">
-        <v>bihar</v>
-      </c>
-      <c r="J2" t="str">
-        <v>munger</v>
-      </c>
-      <c r="K2" t="str">
-        <v>81332</v>
-      </c>
-      <c r="L2" t="str">
-        <v>testing landmark</v>
-      </c>
-      <c r="M2" t="str">
-        <v>Rishikesh Kumar Singh</v>
-      </c>
-      <c r="N2">
-        <v>6207654176</v>
-      </c>
-      <c r="O2" t="str">
-        <v>rishu@gmail.com</v>
-      </c>
-      <c r="P2" t="str">
-        <v>Sector 6 Road, 3rd Floor, Plot No. 10, LSC-02, Sector 06, Dwarka, Delhi 110075, IN</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>NEAR HDFC BANK</v>
-      </c>
-      <c r="R2" t="str">
-        <v>India</v>
-      </c>
-      <c r="S2" t="str">
-        <v>DELHI</v>
-      </c>
-      <c r="T2" t="str">
-        <v>NEW DELHI</v>
-      </c>
-      <c r="U2">
+        <v>1234567890</v>
+      </c>
+      <c r="D2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K2" t="s">
+        <v>63</v>
+      </c>
+      <c r="L2">
         <v>110075</v>
       </c>
-      <c r="V2" t="str">
-        <v>2UD5UIK9S</v>
-      </c>
-      <c r="W2" t="str">
-        <v>amazon</v>
-      </c>
-      <c r="X2" t="str">
-        <v>[{"name":"Reebok Shoes","price":500,"quantity":5,"sku_code":"TBL-WHT-48X36-03"},{"name":"Noise Colorfit Icon 2 1.8'' Display with Bluetooth Calling, AI Voice Assistant Smartwatch  (Blue Strap, Regular)","price":200,"quantity":10,"sku_code":"SHO-BLU-M10-001"},{"name":"Noise Crew 1.38 Round Display with Bluetooth Calling, Metallic finish, IP68 Rating Smartwatch  (Black Strap, Regular)","price":300,"quantity":12,"sku_code":"CAT-RED-LG-001"}]</v>
-      </c>
-      <c r="Y2" t="str">
-        <v>prepaid</v>
-      </c>
-      <c r="Z2">
+      <c r="M2" t="s">
+        <v>64</v>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" t="s">
+        <v>56</v>
+      </c>
+      <c r="P2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>56</v>
+      </c>
+      <c r="R2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" t="s">
+        <v>56</v>
+      </c>
+      <c r="T2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U2" t="s">
+        <v>56</v>
+      </c>
+      <c r="V2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W2" t="s">
+        <v>56</v>
+      </c>
+      <c r="X2" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH2">
+        <v>469</v>
+      </c>
+      <c r="AI2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AO2">
         <v>0</v>
       </c>
-      <c r="AA2">
+      <c r="AP2">
         <v>0</v>
       </c>
-      <c r="AB2" t="str">
-        <v>5.43</v>
-      </c>
-      <c r="AC2" t="str">
-        <v>12.23</v>
-      </c>
-      <c r="AD2" t="str">
-        <v>4.54</v>
-      </c>
-      <c r="AE2" t="str">
-        <v>3.21</v>
-      </c>
-      <c r="AF2">
+      <c r="AQ2">
         <v>0</v>
       </c>
-      <c r="AG2" t="str">
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <v>0.5</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AY2">
         <v>10</v>
       </c>
-      <c r="AH2">
-        <v>1</v>
-      </c>
-      <c r="AI2" t="str">
-        <v/>
-      </c>
-      <c r="AJ2">
-        <v>10</v>
-      </c>
-      <c r="AK2">
+      <c r="AZ2">
         <v>20</v>
       </c>
-      <c r="AL2">
+      <c r="BA2">
         <v>30</v>
       </c>
-      <c r="AM2" t="str">
-        <v>new</v>
+      <c r="BB2">
+        <v>469</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AM2"/>
+    <ignoredError sqref="A1:BA1 B2:BC2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>